--- a/spreadsheet/GPU.xlsx
+++ b/spreadsheet/GPU.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/colinbaird/Projects/GPU/spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F962D1A-F359-704C-80CA-6ABBF52C2A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E1CDE4-4A0D-9345-ABA8-5DB42115A720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{E2A779C8-E5DB-664A-84A6-0EAC9E7554FD}"/>
+    <workbookView xWindow="14820" yWindow="660" windowWidth="15420" windowHeight="18980" xr2:uid="{E2A779C8-E5DB-664A-84A6-0EAC9E7554FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="7" r:id="rId1"/>
     <sheet name="Execution Model" sheetId="8" r:id="rId2"/>
+    <sheet name="Resource Check" sheetId="9" r:id="rId3"/>
+    <sheet name="Roofline" sheetId="10" r:id="rId4"/>
+    <sheet name="Latency Hiding" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,6 +44,213 @@
     <author>Colin Baird</author>
   </authors>
   <commentList>
+    <comment ref="C44" authorId="0" shapeId="0" xr:uid="{156F94FF-E621-4943-AC8A-1259F676B8C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Set to 1 if the multiply unit does fused MAC (like dp4a: multiply + accumulate in one instruction). Set to 0 if accumulate requires separate ALU instructions.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0" xr:uid="{40A36EDC-B414-3B4C-B3E1-5D6854920196}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Pointer bumps and index calculations per inner-loop iteration. Typically 2 (one for A tile pointer, one for B tile pointer).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{2FDA5C08-55B5-1241-A95D-F9CE77B73F8E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Derived: CEIL((T_m×T_k + T_k×T_n) / T_warp). Each iteration loads a T_m×T_k tile of A and a T_k×T_n tile of B (INT8, 1 byte each). Each warp load instruction loads T_warp bytes.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0" xr:uid="{01A513D1-69F7-0E42-8589-3F914DC36DBD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Derived: CEIL(T_m </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>×</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> T_n </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>×</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> T_k / (T_warp </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>×</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> int8_pack)). Each warp multiply instruction processes T_warp lanes, each lane packs B_mul/8 INT8 ops.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{91CB7151-0381-9649-A70A-0EC9ECBD4D1B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Derived: If fused MAC (fused_mac=1), ALU = just address ops. If not fused (fused_mac=0), ALU = I_mul accumulate instructions + address ops.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="0" shapeId="0" xr:uid="{87A25EE3-24D2-9745-855F-13D96159DD4D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Derived: CEIL(T_m*T_n / T_warp). Writes T_m*T_n INT32 output elements. Each warp store instruction handles T_warp elements.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Colin Baird</author>
+  </authors>
+  <commentList>
     <comment ref="E6" authorId="0" shapeId="0" xr:uid="{98D12A3B-6BAC-AB48-9381-8C91D645F5B2}">
       <text>
         <r>
@@ -171,6 +381,20 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t>Per-warp exposed stalls after latency hiding. Other warps' compute (on shared FUs) overlaps this warp's memory latency.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0" shapeId="0" xr:uid="{B68761AA-AA29-2F48-9937-BC0C0698D935}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t>Colin Baird:</t>
         </r>
         <r>
@@ -181,7 +405,493 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Other warps can execute while one is stalled on a miss. (N_warps-1) warps provide compute to hide latency.</t>
+Average wall-clock cycles per iteration per warp, accounting for memory latency hiding by other warps</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{B1043906-2FD4-ED4C-AC5D-76E832406135}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Per batch: all warps serialize on FUs (N_warps </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>×</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> T_iter_compute per iteration), plus any per-warp exposed memory stalls aggregated across warps, plus writeback.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{4EEEBFC2-C8C4-2A4B-BACE-BB4598F2500C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Peak throughput if all multiply lanes busy every cycle, fully pipelined, with INT8 packing. Factor of 2 because each MAC counts as 2 operations (multiply + accumulate) to match ops_total definition.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{E593A231-D3E4-8148-BBEF-6F73324FABDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Fraction of peak compute actually achieved</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{84A7ED3B-79CD-7D45-976D-E139E40DBEA3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+This means the instruction mix parameters imply fewer compute cycles than the workload requires. Increase I_mul or check that ops_total = 2×M×N×K matches the actual instruction encoding.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E54" authorId="0" shapeId="0" xr:uid="{E1FD305D-56C4-B849-898D-DA427C073C17}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+If util_compute &gt; util_bw, the kernel is spending more of its potential on compute than memory, meaning memory is the bottleneck (and vice versa). This is a simplified heuristic.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Colin Baird</author>
+  </authors>
+  <commentList>
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{C518D02B-FB44-7C4E-8D60-5D4D81020974}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Each 18Kb BRAM = 18,432 bits. Rough estimate; actual depends on address mapping and port width.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{B45EDC0D-107A-8746-A37B-C0762EB6E34E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Data array only; tag RAM not included. Actual usage slightly higher.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{4EBF3E52-7260-F641-97FB-FED09EEB6A79}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Hardcoded assumption: 2KB instruction cache</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{B6AC85DE-EA52-D945-99F7-003793235958}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Hardcoded assumption: 4KB for activation function lookup tables</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{45729F6D-7D9A-7D4E-AE46-48209419347D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Each pipeline stage per lane needs a DSP slice. Rough upper bound; actual depends on packing and FPGA DSP native width vs B_mul.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Colin Baird</author>
+  </authors>
+  <commentList>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{C124DF66-3177-A34F-85FE-3AFECD91EED3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Includes cache effects. Higher = more compute per byte fetched.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{77C41AAF-F33E-6143-8A04-A62BEB8A512F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+At this operational intensity, the kernel transitions from memory-bound to compute-bound</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{F5FAD1A7-DDD2-8541-B9C8-D07EB93F77CA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+The roofline bound: the lower of what compute can deliver and what memory can feed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{4961C32B-660A-BC43-8E9D-49241F9D56F3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+How close the kernel gets to the roofline-predicted maximum</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Colin Baird</author>
+  </authors>
+  <commentList>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{2CA0F496-96DE-D448-9659-80FB6D854B97}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+While one warp stalls on a cache miss, other resident warps can execute, providing this many cycles of useful work to overlap with the memory latency.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{723F5297-BE39-3242-BA4C-96C090694845}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+The +1 accounts for the stalled warp itself. This is the minimum warp count for zero exposed memory stall.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{268049E5-3CE9-4C48-9E0B-B0871A2E4E25}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Negative means you need more warps to fully hide memory latency. Consider increasing N_warps in Parameters.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{9EBB83F4-43B1-014A-AC08-C2045A98A769}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Ratio of compute available from other warps to total memory latency. Values below 1.0 mean the SM stalls waiting for DRAM.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{F81D20D2-19F8-174F-A47A-31B42383944D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Colin Baird:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0% = all latency hidden. Higher values mean warps are idle waiting for DRAM.</t>
         </r>
       </text>
     </comment>
@@ -190,7 +900,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="354">
   <si>
     <t>Parameter</t>
   </si>
@@ -393,9 +1103,6 @@
     <t>MEMORY SYSTEM</t>
   </si>
   <si>
-    <t>FPGA BRAM (18Kb blocks) available</t>
-  </si>
-  <si>
     <t>Native bitwidth of each multiply lane</t>
   </si>
   <si>
@@ -507,9 +1214,6 @@
     <t>Loaded per iteration</t>
   </si>
   <si>
-    <t>INSTRUCTION MIX PER INNER-LOOP ITERATION</t>
-  </si>
-  <si>
     <t>Load instructions per iteration</t>
   </si>
   <si>
@@ -519,9 +1223,6 @@
     <t>instructions</t>
   </si>
   <si>
-    <t>Loading A tile + B tile</t>
-  </si>
-  <si>
     <t>Store instructions per iteration</t>
   </si>
   <si>
@@ -537,18 +1238,12 @@
     <t>I_mul</t>
   </si>
   <si>
-    <t>T_m × T_n INT8 multiplies, packed</t>
-  </si>
-  <si>
     <t>ALU instructions per iteration</t>
   </si>
   <si>
     <t>I_alu</t>
   </si>
   <si>
-    <t>Accumulates + address arithmetic</t>
-  </si>
-  <si>
     <t>Divide instructions per iteration</t>
   </si>
   <si>
@@ -564,9 +1259,6 @@
     <t>I_store_wb</t>
   </si>
   <si>
-    <t>Writing output tile to memory</t>
-  </si>
-  <si>
     <t>Weight load fraction</t>
   </si>
   <si>
@@ -807,9 +1499,6 @@
     <t>misses_iter × L_l1_miss</t>
   </si>
   <si>
-    <t>Memory cycles exposed (after latency hiding)</t>
-  </si>
-  <si>
     <t>mem_cycles_exposed</t>
   </si>
   <si>
@@ -817,16 +1506,477 @@
   </si>
   <si>
     <t>SECTION D: EFFECTIVE ITERATION TIME (with Memory Stalls)</t>
+  </si>
+  <si>
+    <t>Effective iteration time</t>
+  </si>
+  <si>
+    <t>T_iter_effective</t>
+  </si>
+  <si>
+    <t>T_iter_compute + memory_cycles_exposed</t>
+  </si>
+  <si>
+    <t>SECTION E: TOTAL KERNEL EXECUTION</t>
+  </si>
+  <si>
+    <t>Number of output tiles</t>
+  </si>
+  <si>
+    <t>N_tiles</t>
+  </si>
+  <si>
+    <t>tiles</t>
+  </si>
+  <si>
+    <t>CEIL(M/T_m) × CEIL(N/T_n)</t>
+  </si>
+  <si>
+    <t>Inner loop iterations per tile</t>
+  </si>
+  <si>
+    <t>iters_per_tile</t>
+  </si>
+  <si>
+    <t>iterations</t>
+  </si>
+  <si>
+    <t>CEIL(K/T_k)</t>
+  </si>
+  <si>
+    <t>Writeback cycles per tile</t>
+  </si>
+  <si>
+    <t>T_writeback</t>
+  </si>
+  <si>
+    <t>I_store_wb × drain_ldst</t>
+  </si>
+  <si>
+    <t>Tile batches (across resident warps)</t>
+  </si>
+  <si>
+    <t>tile_batches</t>
+  </si>
+  <si>
+    <t>batches</t>
+  </si>
+  <si>
+    <t>CEIL(N_tiles / N_warps)</t>
+  </si>
+  <si>
+    <t>Total kernel cycles</t>
+  </si>
+  <si>
+    <t>T_kernel</t>
+  </si>
+  <si>
+    <t>Wall-clock time</t>
+  </si>
+  <si>
+    <t>T_wall</t>
+  </si>
+  <si>
+    <t>seconds</t>
+  </si>
+  <si>
+    <t>T_kernel / (f_clk × 10⁶)</t>
+  </si>
+  <si>
+    <t>T_wall_us</t>
+  </si>
+  <si>
+    <t>µs</t>
+  </si>
+  <si>
+    <t>Converted to microseconds</t>
+  </si>
+  <si>
+    <t>SECTION F: THROUGHPUT METRICS</t>
+  </si>
+  <si>
+    <t>Total INT8 MACs in matmul</t>
+  </si>
+  <si>
+    <t>ops_total</t>
+  </si>
+  <si>
+    <t>operations</t>
+  </si>
+  <si>
+    <t>2 × M × N × K (multiply + accumulate per element)</t>
+  </si>
+  <si>
+    <t>Achieved throughput</t>
+  </si>
+  <si>
+    <t>GOPS</t>
+  </si>
+  <si>
+    <t>ops_total / T_wall / 10⁹</t>
+  </si>
+  <si>
+    <t>GOPS_peak</t>
+  </si>
+  <si>
+    <t>Compute utilization</t>
+  </si>
+  <si>
+    <t>util_compute</t>
+  </si>
+  <si>
+    <t>GOPS / GOPS_peak</t>
+  </si>
+  <si>
+    <t>SECTION G: MEMORY BANDWIDTH ANALYSIS</t>
+  </si>
+  <si>
+    <t>Total cache line fetches from DRAM</t>
+  </si>
+  <si>
+    <t>total_CL_fetches</t>
+  </si>
+  <si>
+    <t>fetches</t>
+  </si>
+  <si>
+    <t>N_tiles × iters_per_tile × loads_total × CL_per_load × miss_rate</t>
+  </si>
+  <si>
+    <t>Total bytes from DRAM</t>
+  </si>
+  <si>
+    <t>total_bytes_dram</t>
+  </si>
+  <si>
+    <t>total_CL_fetches × S_line</t>
+  </si>
+  <si>
+    <t>Bandwidth required</t>
+  </si>
+  <si>
+    <t>BW_required</t>
+  </si>
+  <si>
+    <t>bytes/s</t>
+  </si>
+  <si>
+    <t>total_bytes_dram / T_wall</t>
+  </si>
+  <si>
+    <t>BW_req_GBs</t>
+  </si>
+  <si>
+    <t>Converted to GB/s for comparison</t>
+  </si>
+  <si>
+    <t>Bandwidth utilization</t>
+  </si>
+  <si>
+    <t>util_bw</t>
+  </si>
+  <si>
+    <t>BW_required / BW_dram</t>
+  </si>
+  <si>
+    <t>Bottleneck determination</t>
+  </si>
+  <si>
+    <t>Compares compute utilization vs bandwidth utilization</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>BRAM USAGE (18Kb blocks)</t>
+  </si>
+  <si>
+    <t>Register file total bits</t>
+  </si>
+  <si>
+    <t>N_warps × T_warp × N_regs × 32</t>
+  </si>
+  <si>
+    <t>Register file BRAM blocks</t>
+  </si>
+  <si>
+    <t>L1 cache BRAM blocks</t>
+  </si>
+  <si>
+    <t>Instruction cache size (assumed)</t>
+  </si>
+  <si>
+    <t>2 KB</t>
+  </si>
+  <si>
+    <t>Instruction cache BRAM blocks</t>
+  </si>
+  <si>
+    <t>CEIL(I$ × 8192 / 18432)</t>
+  </si>
+  <si>
+    <t>LUT storage size (assumed)</t>
+  </si>
+  <si>
+    <t>4 KB</t>
+  </si>
+  <si>
+    <t>LUT BRAM blocks</t>
+  </si>
+  <si>
+    <t>CEIL(LUT × 8192 / 18432)</t>
+  </si>
+  <si>
+    <t>TOTAL BRAM used</t>
+  </si>
+  <si>
+    <t>BRAM available</t>
+  </si>
+  <si>
+    <t>DSP SLICE USAGE</t>
+  </si>
+  <si>
+    <t>Multiply unit DSP slices</t>
+  </si>
+  <si>
+    <t>W_mul × L_mul</t>
+  </si>
+  <si>
+    <t>TOTAL DSP used</t>
+  </si>
+  <si>
+    <t>DSP available</t>
+  </si>
+  <si>
+    <t>OPERATIONAL INTENSITY</t>
+  </si>
+  <si>
+    <t>Total arithmetic operations</t>
+  </si>
+  <si>
+    <t>ops</t>
+  </si>
+  <si>
+    <t>2 × M × N × K (from Execution Model)</t>
+  </si>
+  <si>
+    <t>Total DRAM bytes transferred</t>
+  </si>
+  <si>
+    <t>From Execution Model Section G</t>
+  </si>
+  <si>
+    <t>Operational Intensity</t>
+  </si>
+  <si>
+    <t>ops/byte</t>
+  </si>
+  <si>
+    <t>Arithmetic ops per byte of DRAM traffic (as actually executed)</t>
+  </si>
+  <si>
+    <t>RIDGE POINT</t>
+  </si>
+  <si>
+    <t>Peak compute (GOPS)</t>
+  </si>
+  <si>
+    <t>From Execution Model Section F</t>
+  </si>
+  <si>
+    <t>DRAM bandwidth</t>
+  </si>
+  <si>
+    <t>From Parameters</t>
+  </si>
+  <si>
+    <t>Ridge Point</t>
+  </si>
+  <si>
+    <t>OI where compute and BW are balanced</t>
+  </si>
+  <si>
+    <t>ROOFLINE ANALYSIS</t>
+  </si>
+  <si>
+    <t>Achievable GOPS</t>
+  </si>
+  <si>
+    <t>MIN(peak_compute, OI × BW_dram)</t>
+  </si>
+  <si>
+    <t>Achieved GOPS</t>
+  </si>
+  <si>
+    <t>Roofline Efficiency</t>
+  </si>
+  <si>
+    <t>Achieved / Achievable under roofline model</t>
+  </si>
+  <si>
+    <t>Regime</t>
+  </si>
+  <si>
+    <t>Plain-text determination of compute vs memory bound</t>
+  </si>
+  <si>
+    <t>WARP LATENCY HIDING ANALYSIS</t>
+  </si>
+  <si>
+    <t>Compute cycles per warp per iteration</t>
+  </si>
+  <si>
+    <t>T_iter_compute from Execution Model</t>
+  </si>
+  <si>
+    <t>Memory latency to hide per iteration</t>
+  </si>
+  <si>
+    <t>Compute available from other warps</t>
+  </si>
+  <si>
+    <t>(N_warps - 1) × T_iter_compute</t>
+  </si>
+  <si>
+    <t>Warps needed to fully hide memory latency</t>
+  </si>
+  <si>
+    <t>CEIL(mem_latency / compute_per_warp) + 1</t>
+  </si>
+  <si>
+    <t>Current resident warps</t>
+  </si>
+  <si>
+    <t>N_warps from Parameters</t>
+  </si>
+  <si>
+    <t>Surplus / deficit warps</t>
+  </si>
+  <si>
+    <t>N_warps - warps_needed. Positive = surplus; negative = deficit</t>
+  </si>
+  <si>
+    <t>Memory latency coverage ratio</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>≥ 1.0 means full hiding; &lt; 1.0 means exposed stalls</t>
+  </si>
+  <si>
+    <t>SUMMARY</t>
+  </si>
+  <si>
+    <t>Exposed memory stall cycles per iteration</t>
+  </si>
+  <si>
+    <t>From Execution Model Section C</t>
+  </si>
+  <si>
+    <t>Stall as % of effective iteration time</t>
+  </si>
+  <si>
+    <t>What fraction of wall-clock time is pure memory stall</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Plain-text assessment of warp sufficiency</t>
+  </si>
+  <si>
+    <t>Peak INT8 throughput</t>
+  </si>
+  <si>
+    <t>int8_ops_per_cycle × 2 × f_clk (each MAC = 2 ops: mul + add)</t>
+  </si>
+  <si>
+    <t>⚠ Utilization check</t>
+  </si>
+  <si>
+    <t>If utilization &gt; 100%, the instruction count is inconsistent with ops_total</t>
+  </si>
+  <si>
+    <t>Cycles per tile batch (N_warps tiles)</t>
+  </si>
+  <si>
+    <t>T_batch</t>
+  </si>
+  <si>
+    <t>tile_batches × T_batch</t>
+  </si>
+  <si>
+    <t>Memory cycles exposed per warp per iter</t>
+  </si>
+  <si>
+    <t>iters×N_warps×(T_iter_compute + mem_exposed) + writeback×N_warps</t>
+  </si>
+  <si>
+    <t>CEIL(T_m×T_n×T_k / (T_warp * int8_pack)) — auto-computed from packing factor</t>
+  </si>
+  <si>
+    <t>INSTRUCTION MIX PER INNER-LOOP ITERATION (derived from tile geometry)</t>
+  </si>
+  <si>
+    <t>Fused multiply-accumulate (MAC)</t>
+  </si>
+  <si>
+    <t>fused_mac</t>
+  </si>
+  <si>
+    <t>0 or 1</t>
+  </si>
+  <si>
+    <t>1 = accumulate fused into multiply; 0 = separate ALU for accumulate</t>
+  </si>
+  <si>
+    <t>Address arithmetic ops per iteration</t>
+  </si>
+  <si>
+    <t>N_addr_ops</t>
+  </si>
+  <si>
+    <t>Pointer updates per iteration (A ptr + B ptr)</t>
+  </si>
+  <si>
+    <t>CEIL((T_m*T_k + T_k*T_n) / T_warp) -- bytes per iter / bytes per warp load</t>
+  </si>
+  <si>
+    <t>(1-fused_mac)*I_mul + N_addr_ops -- accumulates (if not fused) + pointer math</t>
+  </si>
+  <si>
+    <t>CEIL(T_m*T_n / T_warp) -- output elements / elements per warp store</t>
+  </si>
+  <si>
+    <t>FPGA BRAM blocks available</t>
+  </si>
+  <si>
+    <t>FPGA bits per BRAM block</t>
+  </si>
+  <si>
+    <t>CEIL(bits / BRAM block size)</t>
+  </si>
+  <si>
+    <t>CEIL(S_l1 × 8192 / BRAM b size)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -895,6 +2045,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -928,8 +2085,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -944,11 +2102,88 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1281,8 +2516,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAD4C59-1A86-DF47-8609-5A9763FD6FB7}">
-  <dimension ref="A1:F55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAD4C59-1A86-DF47-8609-5A9763FD6FB7}">
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.6640625" customWidth="1"/>
@@ -1293,32 +2528,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1327,7 +2562,7 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>200</v>
       </c>
       <c r="D3" t="s">
@@ -1339,13 +2574,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>350</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5">
-        <v>280</v>
+      <c r="C4" s="6">
+        <v>557</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1361,7 +2596,7 @@
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>220</v>
       </c>
       <c r="D5" t="s">
@@ -1371,15 +2606,26 @@
         <v>12</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6" s="6">
+        <v>10000</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1388,7 +2634,7 @@
       <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>32</v>
       </c>
       <c r="D8" t="s">
@@ -1402,7 +2648,7 @@
       <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>4</v>
       </c>
       <c r="D9" t="s">
@@ -1419,7 +2665,7 @@
       <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>32</v>
       </c>
       <c r="D10" t="s">
@@ -1430,14 +2676,14 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1446,7 +2692,7 @@
       <c r="B13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="6">
         <v>16</v>
       </c>
       <c r="D13" t="s">
@@ -1463,7 +2709,7 @@
       <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="6">
         <v>8</v>
       </c>
       <c r="D14" t="s">
@@ -1480,14 +2726,14 @@
       <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
         <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -1497,7 +2743,7 @@
       <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <v>8</v>
       </c>
       <c r="D16" t="s">
@@ -1508,14 +2754,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
@@ -1524,7 +2770,7 @@
       <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="6">
         <v>1</v>
       </c>
       <c r="D19" t="s">
@@ -1541,7 +2787,7 @@
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="6">
         <v>4</v>
       </c>
       <c r="D20" t="s">
@@ -1558,7 +2804,7 @@
       <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <v>32</v>
       </c>
       <c r="D21" t="s">
@@ -1575,7 +2821,7 @@
       <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <v>1</v>
       </c>
       <c r="D22" t="s">
@@ -1589,7 +2835,7 @@
       <c r="B23" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
         <v>1</v>
       </c>
       <c r="D23" t="s">
@@ -1603,7 +2849,7 @@
       <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <v>2</v>
       </c>
       <c r="D24" t="s">
@@ -1620,7 +2866,7 @@
       <c r="B25" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="6">
         <v>100</v>
       </c>
       <c r="D25" t="s">
@@ -1637,7 +2883,7 @@
       <c r="B26" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="6">
         <v>1</v>
       </c>
       <c r="D26" t="s">
@@ -1648,435 +2894,482 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
         <v>70</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="6">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="5">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>72</v>
-      </c>
-      <c r="E29" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s">
         <v>74</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="6">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
         <v>75</v>
-      </c>
-      <c r="C30" s="5">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
         <v>77</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="6">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="5">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>79</v>
-      </c>
-      <c r="E31" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
         <v>81</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="D32" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>83</v>
-      </c>
-      <c r="E32" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s">
         <v>85</v>
       </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="5">
+      <c r="C33" s="6">
         <v>80</v>
       </c>
       <c r="D33" t="s">
         <v>45</v>
       </c>
       <c r="E33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
         <v>89</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="6">
+        <v>128</v>
+      </c>
+      <c r="D36" t="s">
         <v>90</v>
-      </c>
-      <c r="C36" s="5">
-        <v>128</v>
-      </c>
-      <c r="D36" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" t="s">
         <v>92</v>
       </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="5">
+      <c r="C37" s="6">
         <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" t="s">
         <v>94</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="6">
+        <v>128</v>
+      </c>
+      <c r="D38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" t="s">
         <v>95</v>
-      </c>
-      <c r="C38" s="5">
-        <v>128</v>
-      </c>
-      <c r="D38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
         <v>97</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="6">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" t="s">
         <v>98</v>
-      </c>
-      <c r="C39" s="5">
-        <v>16</v>
-      </c>
-      <c r="D39" t="s">
-        <v>91</v>
-      </c>
-      <c r="E39" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
         <v>100</v>
       </c>
-      <c r="B40" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="5">
+      <c r="C40" s="6">
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" t="s">
         <v>102</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" s="6">
+        <v>16</v>
+      </c>
+      <c r="D41" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="5">
-        <v>16</v>
-      </c>
-      <c r="D41" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="A43" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C44" s="21">
+        <v>1</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C45" s="21">
+        <v>2</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" s="5">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>110</v>
-      </c>
-      <c r="B45" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="5">
-        <v>0</v>
-      </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" t="s">
-        <v>112</v>
-      </c>
+      <c r="E45" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" s="5">
-        <v>4</v>
+        <v>105</v>
+      </c>
+      <c r="C46" s="20">
+        <f>CEILING((C39*C41+C41*C40)/C8,1)</f>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
-        <v>115</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="5">
-        <v>4</v>
+        <v>108</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E47" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
-      </c>
-      <c r="C48" s="5">
-        <v>0</v>
+        <v>111</v>
+      </c>
+      <c r="C48" s="20">
+        <f>CEILING((C39*C40*C41)/(C8*(C15/8)),1)</f>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E48" t="s">
-        <v>121</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="5">
-        <v>4</v>
+        <v>113</v>
+      </c>
+      <c r="C49" s="20">
+        <f>(1-C44)*C48+C45</f>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C50" s="7">
+        <v>115</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="20">
+        <f>CEILING(C39*C40/C8,1)</f>
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="8">
         <v>0.5</v>
       </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>130</v>
-      </c>
-      <c r="B53" t="s">
-        <v>131</v>
-      </c>
-      <c r="C53" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>127</v>
-      </c>
-      <c r="E53" t="s">
-        <v>132</v>
+      <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>133</v>
-      </c>
-      <c r="B54" t="s">
-        <v>134</v>
-      </c>
-      <c r="C54" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="D54" t="s">
-        <v>127</v>
-      </c>
-      <c r="E54" t="s">
-        <v>135</v>
-      </c>
+      <c r="A54" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C55" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="9">
         <v>1</v>
       </c>
-      <c r="D55" t="s">
-        <v>79</v>
-      </c>
-      <c r="E55" t="s">
-        <v>138</v>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FF4738-7327-2149-869F-AF474CE0F6DA}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="51.6640625" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="58.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>141</v>
+      <c r="E1" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="A2" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C3">
         <f>CEILING(Parameters!C8/Parameters!C13,1)</f>
@@ -2086,15 +3379,15 @@
         <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C4">
         <f>CEILING(Parameters!C8/Parameters!C14,1)</f>
@@ -2104,15 +3397,15 @@
         <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C5">
         <f>CEILING(Parameters!C8/Parameters!C16,1)</f>
@@ -2122,15 +3415,15 @@
         <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C6">
         <f>Parameters!C21</f>
@@ -2140,325 +3433,1386 @@
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C7">
         <f>Parameters!C15/8</f>
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C8">
         <f>Parameters!C14*C7</f>
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C9">
-        <f>Parameters!C44+Parameters!C45+Parameters!C46+Parameters!C47+Parameters!C48</f>
-        <v>12</v>
+        <f>Parameters!C46+Parameters!C47+Parameters!C48+Parameters!C49+Parameters!C50</f>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="A11" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C12">
-        <f>Parameters!C47*C3</f>
-        <v>8</v>
+        <f>Parameters!C49*C3</f>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C13">
-        <f>Parameters!C46*C4</f>
-        <v>16</v>
+        <f>Parameters!C48*C4</f>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C14">
-        <f>Parameters!C44*C5</f>
-        <v>16</v>
+        <f>Parameters!C46*C5</f>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
         <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C15">
-        <f>Parameters!C48*C6</f>
+        <f>Parameters!C50*C6</f>
         <v>0</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C16">
         <f>C9</f>
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17">
         <f>MAX(C12,C13,C14,C15,C16)</f>
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
         <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="A19" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C20">
-        <f>Parameters!C44</f>
-        <v>4</v>
+        <f>Parameters!C46</f>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C21">
-        <f>C20*Parameters!C50</f>
-        <v>2</v>
+        <f>C20*Parameters!C52</f>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C22">
-        <f>C20*(1-Parameters!C50)</f>
-        <v>2</v>
+        <f>C20*(1-Parameters!C52)</f>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" t="s">
         <v>188</v>
-      </c>
-      <c r="E22" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
-      </c>
-      <c r="C23">
-        <f>1-(C21/C20*Parameters!C53 + C22/C20*Parameters!C54)</f>
+        <v>190</v>
+      </c>
+      <c r="C23" s="12">
+        <f>1-(C21/C20*Parameters!C55 + C22/C20*Parameters!C56)</f>
         <v>0.7</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24">
-        <f>C20*Parameters!C55*C23</f>
-        <v>2.8</v>
+        <v>193</v>
+      </c>
+      <c r="C24" s="13">
+        <f>C20*Parameters!C57*C23</f>
+        <v>11.2</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E24" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C25">
         <f>C24*Parameters!C25</f>
-        <v>280</v>
+        <v>1120</v>
       </c>
       <c r="D25" t="s">
         <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>336</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C26">
         <f>MAX(0,C25-(Parameters!C9-1)*C17)</f>
-        <v>232</v>
+        <v>736</v>
       </c>
       <c r="D26" t="s">
         <v>45</v>
       </c>
       <c r="E26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29">
+        <f>C17+C26</f>
+        <v>864</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>206</v>
+      </c>
+      <c r="B32" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+      <c r="C32">
+        <f>CEILING(Parameters!C36/Parameters!C39,1)*CEILING(Parameters!C37/Parameters!C40,1)</f>
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="E32" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33">
+        <f>CEILING(Parameters!C38/Parameters!C41,1)</f>
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34">
+        <f>Parameters!C51*C5</f>
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>333</v>
+      </c>
+      <c r="B35" t="s">
+        <v>334</v>
+      </c>
+      <c r="C35">
+        <f>C33*(Parameters!C9*C17+Parameters!C9*C26)+C34*Parameters!C9</f>
+        <v>27776</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36">
+        <f>CEILING(C32/Parameters!C9,1)</f>
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37">
+        <f>C36*C35</f>
+        <v>444416</v>
+      </c>
+      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38" s="14">
+        <f>C37/(Parameters!C3*1000000)</f>
+        <v>2.22208E-3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" t="s">
+        <v>227</v>
+      </c>
+      <c r="C39" s="15">
+        <f>C38*1000000</f>
+        <v>2222.08</v>
+      </c>
+      <c r="D39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E39" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>231</v>
+      </c>
+      <c r="B42" t="s">
+        <v>232</v>
+      </c>
+      <c r="C42" s="16">
+        <f>2*Parameters!C36*Parameters!C37*Parameters!C38</f>
+        <v>4194304</v>
+      </c>
+      <c r="D42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E42" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>235</v>
+      </c>
+      <c r="B43" t="s">
+        <v>236</v>
+      </c>
+      <c r="C43" s="17">
+        <f>IF(C38=0,0,C42/C38/1000000000)</f>
+        <v>1.8875576036866359</v>
+      </c>
+      <c r="D43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>329</v>
+      </c>
+      <c r="B44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" s="17">
+        <f>C8*2*Parameters!C3*1000000/1000000000</f>
+        <v>12.8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>239</v>
+      </c>
+      <c r="B45" t="s">
+        <v>240</v>
+      </c>
+      <c r="C45" s="12">
+        <f>IF(C44=0,0,C43/C44)</f>
+        <v>0.14746543778801843</v>
+      </c>
+      <c r="D45" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C46" t="str">
+        <f>IF(C45&gt;1,"WARNING: util &gt; 1.0 — instruction mix (I_mul="&amp;Parameters!C48&amp;") may be too low for "&amp;TEXT(C42,"#,##0")&amp;" total ops. Check I_mul.","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="E46" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>243</v>
+      </c>
+      <c r="B48" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" s="15">
+        <f>C32*C33*C20*Parameters!C57*C23</f>
+        <v>5734.4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>247</v>
+      </c>
+      <c r="B49" t="s">
+        <v>248</v>
+      </c>
+      <c r="C49" s="16">
+        <f>C48*Parameters!C30</f>
+        <v>734003.19999999995</v>
+      </c>
+      <c r="D49" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>250</v>
+      </c>
+      <c r="B50" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" s="16">
+        <f>IF(C38=0,0,C49/C38)</f>
+        <v>330322580.64516127</v>
+      </c>
+      <c r="D50" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>250</v>
+      </c>
+      <c r="B51" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="17">
+        <f>C50/1000000000</f>
+        <v>0.33032258064516129</v>
+      </c>
+      <c r="D51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" s="12">
+        <f>IF(Parameters!C32=0,0,C51/Parameters!C32)</f>
+        <v>0.1032258064516129</v>
+      </c>
+      <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C54" t="str">
+        <f>IF(C45&gt;C52,"COMPUTE-BOUND",IF(C52&gt;C45,"MEMORY-BOUND","BALANCED"))</f>
+        <v>COMPUTE-BOUND</v>
+      </c>
+      <c r="E54" t="s">
+        <v>260</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C54">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="MEMORY-BOUND">
+      <formula>NOT(ISERROR(SEARCH("MEMORY-BOUND",C54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C54">
+    <cfRule type="containsText" priority="2" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",C54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",C46)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46">
+    <cfRule type="containsText" priority="4" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",C46)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39248061-8A09-854D-BFFE-A81D1AEB9874}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="41.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="46.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10"/>
+      <c r="B1" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="16">
+        <f>Parameters!C9*Parameters!C8*Parameters!C10*32</f>
+        <v>131072</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4">
+        <f>CEILING(C3/Parameters!C6,1)</f>
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5">
+        <f>CEILING(Parameters!C29*1024*8/Parameters!C6,1)</f>
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7">
+        <f>CEILING(C6*1024*8/Parameters!C6,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9">
+        <f>CEILING(C8*1024*8/Parameters!C6,1)</f>
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="1">
+        <f>C4+C5+C7+C9</f>
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f>IF(C11&lt;=Parameters!C4,"WITHIN BUDGET","OVER BUDGET")</f>
+        <v>WITHIN BUDGET</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12">
+        <f>Parameters!C4</f>
+        <v>557</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="str">
+        <f>"Headroom: "&amp;TEXT(Parameters!C4-C11,"#,##0")&amp;" blocks ("&amp;TEXT((Parameters!C4-C11)/Parameters!C4,"0.0%")&amp;")"</f>
+        <v>Headroom: 533 blocks (95.7%)</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15">
+        <f>Parameters!C14*Parameters!C20</f>
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" s="1">
+        <f>C15</f>
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <f>IF(C17&lt;=Parameters!C5,"WITHIN BUDGET","OVER BUDGET")</f>
+        <v>WITHIN BUDGET</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>282</v>
+      </c>
+      <c r="C18">
+        <f>Parameters!C5</f>
+        <v>220</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="str">
+        <f>"Headroom: "&amp;TEXT(Parameters!C5-C17,"#,##0")&amp;" slices ("&amp;TEXT((Parameters!C5-C17)/Parameters!C5,"0.0%")&amp;")"</f>
+        <v>Headroom: 188 slices (85.5%)</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="OVER">
+      <formula>NOT(ISERROR(SEARCH("OVER",E11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="containsText" priority="2" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",E11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="OVER">
+      <formula>NOT(ISERROR(SEARCH("OVER",E17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="containsText" priority="4" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",E17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A552CC-14D0-4B42-9A41-94DB3C0ED113}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+    <col min="2" max="2" width="66.6640625" customWidth="1"/>
+    <col min="4" max="4" width="58.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="16">
+        <f>'Execution Model'!C42</f>
+        <v>4194304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" s="16">
+        <f>'Execution Model'!C49</f>
+        <v>734003.19999999995</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="18">
+        <f>IF(B4=0,0,B3/B4)</f>
+        <v>5.7142857142857144</v>
+      </c>
+      <c r="C5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="12">
+        <f>'Execution Model'!C44</f>
+        <v>12.8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9">
+        <f>Parameters!C32</f>
+        <v>3.2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B10" s="18">
+        <f>IF(B9=0,0,B8/B9)</f>
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="12">
+        <f>MIN(B8,B5*B9)</f>
+        <v>12.8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="12">
+        <f>'Execution Model'!C43</f>
+        <v>1.8875576036866359</v>
+      </c>
+      <c r="C14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="12">
+        <f>IF(B13=0,0,B14/B13)</f>
+        <v>0.14746543778801843</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(B5&gt;=B10,"COMPUTE-BOUND: OI (×"&amp;TEXT(B5,"0.0")&amp;") ≥ Ridge Point (×"&amp;TEXT(B10,"0.0")&amp;")","MEMORY-BOUND: OI (×"&amp;TEXT(B5,"0.0")&amp;") &lt; Ridge Point (×"&amp;TEXT(B10,"0.0")&amp;")")</f>
+        <v>COMPUTE-BOUND: OI (×5.7) ≥ Ridge Point (×4.0)</v>
+      </c>
+      <c r="D17" t="s">
+        <v>306</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="MEMORY-BOUND">
+      <formula>NOT(ISERROR(SEARCH("MEMORY-BOUND",B17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="containsText" priority="2" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",B17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD9A4384-05B4-664F-B2C7-71AE67EA2356}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="46.6640625" customWidth="1"/>
+    <col min="2" max="2" width="66.6640625" customWidth="1"/>
+    <col min="4" max="4" width="58.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B3">
+        <f>'Execution Model'!C17</f>
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4">
+        <f>'Execution Model'!C25</f>
+        <v>1120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5">
+        <f>(Parameters!C9-1)*B3</f>
+        <v>384</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7">
+        <f>IF(B4=0,1,CEILING(B4/B3,1)+1)</f>
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8">
+        <f>Parameters!C9</f>
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9">
+        <f>B8-B7</f>
+        <v>-6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" s="12">
+        <f>IF(B4=0,1,B5/B4)</f>
+        <v>0.34285714285714286</v>
+      </c>
+      <c r="C11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>323</v>
+      </c>
+      <c r="B14">
+        <f>'Execution Model'!C26</f>
+        <v>736</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="19">
+        <f>IF('Execution Model'!C29=0,0,B14/'Execution Model'!C29)</f>
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(B11&gt;=1,"SUFFICIENT: "&amp;TEXT(B8,"0")&amp;" warps provide full latency coverage (ratio "&amp;TEXT(B11,"0.00")&amp;")","INSUFFICIENT: Need "&amp;TEXT(B7,"0")&amp;" warps but have "&amp;TEXT(B8,"0")&amp;" (ratio "&amp;TEXT(B11,"0.00")&amp;")")</f>
+        <v>INSUFFICIENT: Need 10 warps but have 4 (ratio 0.34)</v>
+      </c>
+      <c r="D16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="INSUFFICIENT">
+      <formula>NOT(ISERROR(SEARCH("INSUFFICIENT",B16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="containsText" priority="2" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",B16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/spreadsheet/GPU.xlsx
+++ b/spreadsheet/GPU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/colinbaird/Projects/GPU/spreadsheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E1CDE4-4A0D-9345-ABA8-5DB42115A720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACD4F91-B559-D64A-BB7D-07E41AE29B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="660" windowWidth="15420" windowHeight="18980" xr2:uid="{E2A779C8-E5DB-664A-84A6-0EAC9E7554FD}"/>
+    <workbookView xWindow="14820" yWindow="660" windowWidth="15420" windowHeight="18980" activeTab="2" xr2:uid="{E2A779C8-E5DB-664A-84A6-0EAC9E7554FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Roofline" sheetId="10" r:id="rId4"/>
     <sheet name="Latency Hiding" sheetId="11" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +31,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -2163,23 +2164,23 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2196,14 +2197,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2241,7 +2238,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2347,7 +2344,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2489,7 +2486,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2649,7 +2646,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -2911,7 +2908,7 @@
         <v>70</v>
       </c>
       <c r="C29" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
         <v>71</v>
@@ -3733,7 +3730,7 @@
       </c>
       <c r="C26">
         <f>MAX(0,C25-(Parameters!C9-1)*C17)</f>
-        <v>736</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
         <v>45</v>
@@ -3760,7 +3757,7 @@
       </c>
       <c r="C29">
         <f>C17+C26</f>
-        <v>864</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
@@ -3841,7 +3838,7 @@
       </c>
       <c r="C35">
         <f>C33*(Parameters!C9*C17+Parameters!C9*C26)+C34*Parameters!C9</f>
-        <v>27776</v>
+        <v>16896</v>
       </c>
       <c r="D35" t="s">
         <v>45</v>
@@ -3859,7 +3856,7 @@
       </c>
       <c r="C36">
         <f>CEILING(C32/Parameters!C9,1)</f>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
         <v>219</v>
@@ -3877,7 +3874,7 @@
       </c>
       <c r="C37">
         <f>C36*C35</f>
-        <v>444416</v>
+        <v>67584</v>
       </c>
       <c r="D37" t="s">
         <v>45</v>
@@ -3895,7 +3892,7 @@
       </c>
       <c r="C38" s="14">
         <f>C37/(Parameters!C3*1000000)</f>
-        <v>2.22208E-3</v>
+        <v>3.3792000000000002E-4</v>
       </c>
       <c r="D38" t="s">
         <v>225</v>
@@ -3913,7 +3910,7 @@
       </c>
       <c r="C39" s="15">
         <f>C38*1000000</f>
-        <v>2222.08</v>
+        <v>337.92</v>
       </c>
       <c r="D39" t="s">
         <v>228</v>
@@ -3958,7 +3955,7 @@
       </c>
       <c r="C43" s="17">
         <f>IF(C38=0,0,C42/C38/1000000000)</f>
-        <v>1.8875576036866359</v>
+        <v>12.412121212121212</v>
       </c>
       <c r="D43" t="s">
         <v>236</v>
@@ -3994,7 +3991,7 @@
       </c>
       <c r="C45" s="12">
         <f>IF(C44=0,0,C43/C44)</f>
-        <v>0.14746543778801843</v>
+        <v>0.96969696969696961</v>
       </c>
       <c r="D45" t="s">
         <v>121</v>
@@ -4069,7 +4066,7 @@
       </c>
       <c r="C50" s="16">
         <f>IF(C38=0,0,C49/C38)</f>
-        <v>330322580.64516127</v>
+        <v>2172121212.121212</v>
       </c>
       <c r="D50" t="s">
         <v>252</v>
@@ -4087,7 +4084,7 @@
       </c>
       <c r="C51" s="17">
         <f>C50/1000000000</f>
-        <v>0.33032258064516129</v>
+        <v>2.1721212121212119</v>
       </c>
       <c r="D51" t="s">
         <v>82</v>
@@ -4105,7 +4102,7 @@
       </c>
       <c r="C52" s="12">
         <f>IF(Parameters!C32=0,0,C51/Parameters!C32)</f>
-        <v>0.1032258064516129</v>
+        <v>0.67878787878787872</v>
       </c>
       <c r="D52" t="s">
         <v>121</v>
@@ -4127,24 +4124,20 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C54">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="MEMORY-BOUND">
-      <formula>NOT(ISERROR(SEARCH("MEMORY-BOUND",C54)))</formula>
+  <conditionalFormatting sqref="C46">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="4" operator="containsText" text="Text">
+      <formula>NOT(ISERROR(SEARCH("Text",C46)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="MEMORY-BOUND">
+      <formula>NOT(ISERROR(SEARCH("MEMORY-BOUND",C54)))</formula>
+    </cfRule>
     <cfRule type="containsText" priority="2" operator="containsText" text="Text">
       <formula>NOT(ISERROR(SEARCH("Text",C54)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",C46)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C46">
-    <cfRule type="containsText" priority="4" operator="containsText" text="Text">
-      <formula>NOT(ISERROR(SEARCH("Text",C46)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4196,7 +4189,7 @@
       </c>
       <c r="C3" s="16">
         <f>Parameters!C9*Parameters!C8*Parameters!C10*32</f>
-        <v>131072</v>
+        <v>524288</v>
       </c>
       <c r="D3" t="s">
         <v>38</v>
@@ -4211,7 +4204,7 @@
       </c>
       <c r="C4">
         <f>CEILING(C3/Parameters!C6,1)</f>
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -4226,7 +4219,7 @@
       </c>
       <c r="C5">
         <f>CEILING(Parameters!C29*1024*8/Parameters!C6,1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -4240,7 +4233,7 @@
         <v>269</v>
       </c>
       <c r="C6" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
         <v>71</v>
@@ -4255,7 +4248,7 @@
       </c>
       <c r="C7">
         <f>CEILING(C6*1024*8/Parameters!C6,1)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -4296,7 +4289,7 @@
       </c>
       <c r="C11" s="1">
         <f>C4+C5+C7+C9</f>
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>11</v>
@@ -4319,7 +4312,7 @@
       </c>
       <c r="E12" t="str">
         <f>"Headroom: "&amp;TEXT(Parameters!C4-C11,"#,##0")&amp;" blocks ("&amp;TEXT((Parameters!C4-C11)/Parameters!C4,"0.0%")&amp;")"</f>
-        <v>Headroom: 533 blocks (95.7%)</v>
+        <v>Headroom: 489 blocks (87.8%)</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -4383,8 +4376,6 @@
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="OVER">
       <formula>NOT(ISERROR(SEARCH("OVER",E11)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
     <cfRule type="containsText" priority="2" operator="containsText" text="Text">
       <formula>NOT(ISERROR(SEARCH("Text",E11)))</formula>
     </cfRule>
@@ -4393,8 +4384,6 @@
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="OVER">
       <formula>NOT(ISERROR(SEARCH("OVER",E17)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
     <cfRule type="containsText" priority="4" operator="containsText" text="Text">
       <formula>NOT(ISERROR(SEARCH("Text",E17)))</formula>
     </cfRule>
@@ -4563,7 +4552,7 @@
       </c>
       <c r="B14" s="12">
         <f>'Execution Model'!C43</f>
-        <v>1.8875576036866359</v>
+        <v>12.412121212121212</v>
       </c>
       <c r="C14" t="s">
         <v>236</v>
@@ -4578,7 +4567,7 @@
       </c>
       <c r="B15" s="12">
         <f>IF(B13=0,0,B14/B13)</f>
-        <v>0.14746543778801843</v>
+        <v>0.96969696969696961</v>
       </c>
       <c r="C15" t="s">
         <v>121</v>
@@ -4604,8 +4593,6 @@
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="MEMORY-BOUND">
       <formula>NOT(ISERROR(SEARCH("MEMORY-BOUND",B17)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
     <cfRule type="containsText" priority="2" operator="containsText" text="Text">
       <formula>NOT(ISERROR(SEARCH("Text",B17)))</formula>
     </cfRule>
@@ -4683,7 +4670,7 @@
       </c>
       <c r="B5">
         <f>(Parameters!C9-1)*B3</f>
-        <v>384</v>
+        <v>1920</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -4713,7 +4700,7 @@
       </c>
       <c r="B8">
         <f>Parameters!C9</f>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -4728,7 +4715,7 @@
       </c>
       <c r="B9">
         <f>B8-B7</f>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
@@ -4743,7 +4730,7 @@
       </c>
       <c r="B11" s="12">
         <f>IF(B4=0,1,B5/B4)</f>
-        <v>0.34285714285714286</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="C11" t="s">
         <v>320</v>
@@ -4766,7 +4753,7 @@
       </c>
       <c r="B14">
         <f>'Execution Model'!C26</f>
-        <v>736</v>
+        <v>0</v>
       </c>
       <c r="C14" t="s">
         <v>45</v>
@@ -4781,7 +4768,7 @@
       </c>
       <c r="B15" s="19">
         <f>IF('Execution Model'!C29=0,0,B14/'Execution Model'!C29)</f>
-        <v>0.85185185185185186</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
         <v>121</v>
@@ -4796,7 +4783,7 @@
       </c>
       <c r="B16" t="str">
         <f>IF(B11&gt;=1,"SUFFICIENT: "&amp;TEXT(B8,"0")&amp;" warps provide full latency coverage (ratio "&amp;TEXT(B11,"0.00")&amp;")","INSUFFICIENT: Need "&amp;TEXT(B7,"0")&amp;" warps but have "&amp;TEXT(B8,"0")&amp;" (ratio "&amp;TEXT(B11,"0.00")&amp;")")</f>
-        <v>INSUFFICIENT: Need 10 warps but have 4 (ratio 0.34)</v>
+        <v>SUFFICIENT: 16 warps provide full latency coverage (ratio 1.71)</v>
       </c>
       <c r="D16" t="s">
         <v>328</v>
@@ -4807,8 +4794,6 @@
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="INSUFFICIENT">
       <formula>NOT(ISERROR(SEARCH("INSUFFICIENT",B16)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
     <cfRule type="containsText" priority="2" operator="containsText" text="Text">
       <formula>NOT(ISERROR(SEARCH("Text",B16)))</formula>
     </cfRule>
